--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -441,7 +441,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q232A</t>
+          <t>S65T</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -451,7 +451,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y233A</t>
+          <t>Y66H</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -461,7 +461,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A40P</t>
+          <t>T203Y</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -471,7 +471,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E61Y</t>
+          <t>F64L</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L150V</t>
+          <t>A206K</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -491,7 +491,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A40P_E61Y</t>
+          <t>S65A</t>
         </is>
       </c>
       <c r="B8" t="n">

--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -441,37 +441,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S65T</t>
+          <t>65A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.85</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y66H</t>
+          <t>203Y</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.48</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T203Y</t>
+          <t>65T</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F64L</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A206K</t>
+          <t>206K</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -491,11 +491,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S65A</t>
+          <t>66H</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.11</v>
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVOLVEpro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EVOLVEpro" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,71 +431,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WT</t>
+          <t>168T</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3.103333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>65A</t>
+          <t>204Y</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.11</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>203Y</t>
+          <t>154T</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.33</v>
+        <v>1.856666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>65T</t>
+          <t>164A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64L</t>
+          <t>100S</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.55</v>
+        <v>1.533333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>206K</t>
+          <t>206T</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>66H</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.48</v>
+        <v>1.196666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>149D</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.053333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>148P</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8833333333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>67H</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4733333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -431,101 +431,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>168T</t>
+          <t>88V</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.103333333333333</v>
+        <v>3.113333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>204Y</t>
+          <t>28A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>154T</t>
+          <t>78A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.856666666666667</v>
+        <v>1.863333333333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>164A</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100S</t>
+          <t>175A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.533333333333333</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>206T</t>
+          <t>150A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>200A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.196666666666667</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>149D</t>
+          <t>163A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.053333333333333</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>148P</t>
+          <t>97A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8833333333333333</v>
+        <v>0.6233333333333334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>67H</t>
+          <t>190A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,40 +491,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>200A</t>
+          <t>163A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>163A</t>
+          <t>97A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.88</v>
+        <v>0.6233333333333334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>97A</t>
+          <t>190A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6233333333333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>190A</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
         <v>0.47</v>
       </c>
     </row>

--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,40 +481,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>150A</t>
+          <t>239A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>163A</t>
+          <t>150A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.88</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>97A</t>
+          <t>163A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6233333333333334</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>97A</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6233333333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>190A</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>0.47</v>
       </c>
     </row>

--- a/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
+++ b/src-tauri/samples/mame/08_mame_evolvepro_raw.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,70 +461,130 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>227V</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>175A</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>239A</t>
+          <t>205A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>150A</t>
+          <t>175A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>163A</t>
+          <t>239A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>97A</t>
+          <t>150A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6233333333333334</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>200A</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>215A</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>163A</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>210A</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>97A</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6233333333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>235A</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>190A</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B17" t="n">
         <v>0.47</v>
       </c>
     </row>
